--- a/ai_scm_project/outputs/reports/llm_token_capacity_2026_2030.xlsx
+++ b/ai_scm_project/outputs/reports/llm_token_capacity_2026_2030.xlsx
@@ -665,7 +665,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Scenario token capacity: Bull/Base/Bear plus grid-constrained case</a:t>
+              <a:t>시나리오별 토큰 capacity: 낙관/기준/보수/전력제약</a:t>
             </a:r>
           </a:p>
         </rich>
